--- a/Vulnerability Test Results/Vulnerability_Report_Post_Remediation.xlsx
+++ b/Vulnerability Test Results/Vulnerability_Report_Post_Remediation.xlsx
@@ -494,12 +494,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:00</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:01</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -526,12 +526,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:00</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:01</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -558,12 +558,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:00</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:01</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -590,12 +590,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:00</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:01</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -622,12 +622,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:00</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:01</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -654,12 +654,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:00</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:01</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -686,12 +686,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:00</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:01</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -718,12 +718,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:00</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-11 14:00:01</t>
+          <t>2026-06-13 12:55:11</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1800,7 +1800,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1821,7 +1820,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1842,7 +1840,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1863,7 +1860,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1884,7 +1880,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1905,7 +1900,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1926,7 +1920,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1947,7 +1940,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1968,7 +1960,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1989,7 +1980,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2010,7 +2000,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2031,7 +2020,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,7 +2040,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2073,7 +2060,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2094,7 +2080,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2115,7 +2100,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2136,7 +2120,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2157,7 +2140,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2178,7 +2160,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2199,7 +2180,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2220,7 +2200,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2241,7 +2220,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2262,7 +2240,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2283,7 +2260,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2304,7 +2280,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2325,7 +2300,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2346,7 +2320,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2367,7 +2340,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2388,7 +2360,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2409,7 +2380,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2430,7 +2400,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2451,7 +2420,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2472,7 +2440,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2493,7 +2460,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2514,7 +2480,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2535,7 +2500,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2556,7 +2520,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2577,7 +2540,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2598,7 +2560,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2619,7 +2580,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2640,7 +2600,6 @@
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
